--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2018_los_rios.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2018_los_rios.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:48</t>
+    <t xml:space="preserve">2026-10-05 02:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>233816.89</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +847,7 @@
         <v>241740.8</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -913,7 +913,7 @@
         <v>241177.41</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -932,7 +932,7 @@
         <v>24</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>245854.12</v>
+        <v>245854.13</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>332082.44</v>
@@ -998,7 +998,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>236308.12</v>
+        <v>236308.13</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>318143.44</v>
@@ -1130,7 +1130,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>251327.62</v>
+        <v>251327.63</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>338820.44</v>
@@ -1152,7 +1152,7 @@
         <v>44</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>255336.62</v>
+        <v>255336.63</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>340767.66</v>
@@ -1287,7 +1287,7 @@
         <v>297265.44</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1295,7 +1295,7 @@
         <v>57</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>295912.12</v>
+        <v>295912.13</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>394159.06</v>
@@ -1361,7 +1361,7 @@
         <v>63</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>339640.62</v>
+        <v>339640.63</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>431783.91</v>
@@ -1529,7 +1529,7 @@
         <v>338010.66</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1581,7 +1581,7 @@
         <v>83</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>360514.12</v>
+        <v>360514.13</v>
       </c>
       <c r="C82" s="2" t="n">
         <v>467154.72</v>
@@ -1595,7 +1595,7 @@
         <v>350297.47</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
